--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_master_protalent.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_master_protalent.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\Out\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_master_protalent" sheetId="1" r:id="rId1"/>
